--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45307</v>
+        <v>44929</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
@@ -1317,38 +1317,38 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44929</v>
+        <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1418,42 +1418,46 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1470,7 +1474,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1483,13 +1487,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1523,46 +1527,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45762</v>
+        <v>45307</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1628,39 +1628,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44957</v>
+        <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44573</v>
+        <v>45762</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45327</v>
+        <v>45722</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1947,8 +1947,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1991,7 +1996,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2001,14 +2006,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45513</v>
+        <v>45846</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2021,7 +2026,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2064,7 +2069,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2078,10 +2083,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45722</v>
+        <v>45099</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2093,13 +2098,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2142,7 +2142,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44930</v>
+        <v>46062</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45589</v>
+        <v>44957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2288,7 +2288,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45846</v>
+        <v>46112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46062</v>
+        <v>44573</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2444,14 +2444,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45694</v>
+        <v>44928</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46112</v>
+        <v>46198</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2580,7 +2580,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44928</v>
+        <v>45327</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2653,7 +2653,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45063</v>
+        <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45099</v>
+        <v>45063</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45327</v>
+        <v>44930</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2882,14 +2882,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45042</v>
+        <v>45513</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 53131-2021</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44468</v>
+        <v>45042</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
         <v>45327</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3101,14 +3101,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45762</v>
+        <v>45694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46198</v>
+        <v>45589</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 53131-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46223</v>
+        <v>44468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>45327</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 2943-2023</t>
+          <t>A 11517-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -933,14 +933,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44945</v>
+        <v>45372</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -953,16 +953,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>11.3</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -977,7 +977,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -989,148 +989,148 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Tvåblad
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 11517-2024 artfynd.xlsx", "A 11517-2024")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 11517-2024 karta.png", "A 11517-2024")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 11517-2024 georefererad karta.tif", "A 11517-2024")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 11517-2024 FSC-klagomål.docx", "A 11517-2024")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 11517-2024 FSC-klagomål mail.docx", "A 11517-2024")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 11517-2024 tillsynsbegäran.docx", "A 11517-2024")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 11517-2024 tillsynsbegäran mail.docx", "A 11517-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 2943-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>44945</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BÅSTAD</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Sårläka
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 2943-2023 artfynd.xlsx", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 2943-2023 karta.png", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 2943-2023 georefererad karta.tif", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 2943-2023 FSC-klagomål.docx", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 2943-2023 FSC-klagomål mail.docx", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 2943-2023 tillsynsbegäran.docx", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 2943-2023 tillsynsbegäran mail.docx", "A 2943-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 11517-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45372</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BÅSTAD</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Tvåblad
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 11517-2024 artfynd.xlsx", "A 11517-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 11517-2024 karta.png", "A 11517-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 11517-2024 georefererad karta.tif", "A 11517-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 11517-2024 FSC-klagomål.docx", "A 11517-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 11517-2024 FSC-klagomål mail.docx", "A 11517-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 11517-2024 tillsynsbegäran.docx", "A 11517-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 11517-2024 tillsynsbegäran mail.docx", "A 11517-2024")</f>
         <v/>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44929</v>
+        <v>45307</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
@@ -1317,31 +1317,31 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45307</v>
+        <v>44929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -1636,31 +1636,31 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45327</v>
+        <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45762</v>
+        <v>46062</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45722</v>
+        <v>44573</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1947,13 +1947,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1996,7 +1991,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2010,10 +2005,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45846</v>
+        <v>45327</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2026,7 +2021,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2069,7 +2064,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2083,10 +2078,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45099</v>
+        <v>45042</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2099,7 +2094,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2142,7 +2137,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2156,10 +2151,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46062</v>
+        <v>46112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2172,7 +2167,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2215,7 +2210,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2225,14 +2220,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44957</v>
+        <v>45513</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2245,7 +2240,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2288,7 +2283,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 53131-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2302,10 +2297,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46112</v>
+        <v>44468</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2318,7 +2313,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2361,7 +2356,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2375,10 +2370,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44573</v>
+        <v>44930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2391,7 +2386,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2434,7 +2429,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2448,10 +2443,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44928</v>
+        <v>45589</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2464,7 +2459,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2507,7 +2502,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2517,14 +2512,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46198</v>
+        <v>45694</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2537,7 +2532,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2580,7 +2575,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2594,10 +2589,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45327</v>
+        <v>44928</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2610,7 +2605,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2653,7 +2648,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2667,10 +2662,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46223</v>
+        <v>45063</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2683,7 +2678,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2726,7 +2721,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2740,10 +2735,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45063</v>
+        <v>45327</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2756,7 +2751,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2799,7 +2794,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2813,10 +2808,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44930</v>
+        <v>45099</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2829,7 +2824,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2867,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2882,14 +2877,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45513</v>
+        <v>45762</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2902,7 +2897,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2945,7 +2940,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2959,10 +2954,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45042</v>
+        <v>45327</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2975,7 +2970,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3018,7 +3013,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3032,10 +3027,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45327</v>
+        <v>46198</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3091,7 +3086,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3101,14 +3096,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45694</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3116,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3164,7 +3159,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3178,10 +3173,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45589</v>
+        <v>45327</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3194,7 +3189,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3237,7 +3232,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 53131-2021</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3251,10 +3246,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44468</v>
+        <v>45722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3266,8 +3261,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3310,7 +3310,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45327</v>
+        <v>45846</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3400,7 +3400,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 11517-2024</t>
+          <t>A 2943-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -933,14 +933,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45372</v>
+        <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -953,16 +953,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>11.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -977,7 +977,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -989,148 +989,148 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sårläka
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 2943-2023 artfynd.xlsx", "A 2943-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 2943-2023 karta.png", "A 2943-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 2943-2023 georefererad karta.tif", "A 2943-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 2943-2023 FSC-klagomål.docx", "A 2943-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 2943-2023 FSC-klagomål mail.docx", "A 2943-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 2943-2023 tillsynsbegäran.docx", "A 2943-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 2943-2023 tillsynsbegäran mail.docx", "A 2943-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 11517-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45372</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BÅSTAD</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Tvåblad
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 11517-2024 artfynd.xlsx", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 11517-2024 karta.png", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 11517-2024 georefererad karta.tif", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 11517-2024 FSC-klagomål.docx", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 11517-2024 FSC-klagomål mail.docx", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 11517-2024 tillsynsbegäran.docx", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 11517-2024 tillsynsbegäran mail.docx", "A 11517-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 2943-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44945</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BÅSTAD</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sårläka
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 2943-2023 artfynd.xlsx", "A 2943-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 2943-2023 karta.png", "A 2943-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 2943-2023 georefererad karta.tif", "A 2943-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 2943-2023 FSC-klagomål.docx", "A 2943-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 2943-2023 FSC-klagomål mail.docx", "A 2943-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 2943-2023 tillsynsbegäran.docx", "A 2943-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 2943-2023 tillsynsbegäran mail.docx", "A 2943-2023")</f>
         <v/>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45307</v>
+        <v>44929</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
@@ -1317,31 +1317,31 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44929</v>
+        <v>45307</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -1636,31 +1636,31 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44957</v>
+        <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46062</v>
+        <v>45762</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.9</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44573</v>
+        <v>45722</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1947,8 +1947,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1991,7 +1996,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2005,10 +2010,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45327</v>
+        <v>45099</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2021,7 +2026,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2064,7 +2069,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2078,10 +2083,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45042</v>
+        <v>45846</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2094,7 +2099,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2137,7 +2142,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2151,10 +2156,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46112</v>
+        <v>44957</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2167,7 +2172,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2210,7 +2215,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2220,14 +2225,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45513</v>
+        <v>44573</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2240,7 +2245,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2283,7 +2288,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 53131-2021</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2297,10 +2302,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44468</v>
+        <v>46062</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2313,7 +2318,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2356,7 +2361,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2370,10 +2375,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44930</v>
+        <v>46112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2386,7 +2391,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2429,7 +2434,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2443,10 +2448,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45589</v>
+        <v>44928</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2459,7 +2464,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2502,7 +2507,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2512,14 +2517,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45694</v>
+        <v>45327</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2532,7 +2537,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2575,7 +2580,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2589,10 +2594,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44928</v>
+        <v>45063</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2605,7 +2610,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2648,7 +2653,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2662,10 +2667,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45063</v>
+        <v>44930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2678,7 +2683,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2721,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2731,14 +2736,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45327</v>
+        <v>45513</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2751,7 +2756,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2794,7 +2799,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2808,10 +2813,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45099</v>
+        <v>45042</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2824,7 +2829,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2867,7 +2872,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2881,10 +2886,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45762</v>
+        <v>45327</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2897,7 +2902,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2940,7 +2945,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2950,14 +2955,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45327</v>
+        <v>45694</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2970,7 +2975,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3013,7 +3018,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3027,10 +3032,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46198</v>
+        <v>45589</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3043,7 +3048,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3086,7 +3091,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 53131-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3100,10 +3105,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46223</v>
+        <v>44468</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3116,7 +3121,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3159,7 +3164,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3173,10 +3178,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45327</v>
+        <v>46198</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3189,7 +3194,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3232,7 +3237,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3246,10 +3251,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45722</v>
+        <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3261,13 +3266,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3310,7 +3310,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45846</v>
+        <v>45327</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3400,7 +3400,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>44929</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1358,14 +1358,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45762</v>
+        <v>45307</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1414,50 +1414,46 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1474,7 +1470,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,13 +1483,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1527,42 +1523,46 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45307</v>
+        <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1628,39 +1628,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45327</v>
+        <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45762</v>
+        <v>44573</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45722</v>
+        <v>45327</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1947,13 +1947,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1996,7 +1991,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2006,14 +2001,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45099</v>
+        <v>45513</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2026,7 +2021,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2069,7 +2064,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2083,10 +2078,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45846</v>
+        <v>45722</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2098,8 +2093,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2142,7 +2142,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44957</v>
+        <v>46062</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>5.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44573</v>
+        <v>44930</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2288,7 +2288,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46062</v>
+        <v>45589</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46112</v>
+        <v>45846</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44928</v>
+        <v>46112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2517,14 +2517,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45327</v>
+        <v>45694</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2580,7 +2580,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45063</v>
+        <v>44928</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2653,7 +2653,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44930</v>
+        <v>45063</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45513</v>
+        <v>45099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45042</v>
+        <v>45327</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45327</v>
+        <v>45042</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2955,14 +2955,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45694</v>
+        <v>46198</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 53131-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45589</v>
+        <v>44468</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53131-2021</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44468</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46198</v>
+        <v>45327</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46223</v>
+        <v>45762</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>45327</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44929</v>
+        <v>45762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1313,42 +1313,46 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1358,14 +1362,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45307</v>
+        <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,13 +1382,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1414,46 +1418,46 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1467,10 +1471,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45762</v>
+        <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1483,7 +1487,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1523,46 +1527,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45762</v>
+        <v>45307</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1628,39 +1628,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44957</v>
+        <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44573</v>
+        <v>45762</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45327</v>
+        <v>45099</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45513</v>
+        <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2064,7 +2064,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45722</v>
+        <v>44573</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2093,13 +2093,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2142,7 +2137,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2156,10 +2151,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46062</v>
+        <v>44928</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2172,7 +2167,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2215,7 +2210,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2229,10 +2224,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44930</v>
+        <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2245,7 +2240,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2288,7 +2283,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2302,10 +2297,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45589</v>
+        <v>45063</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2318,7 +2313,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2361,7 +2356,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2375,10 +2370,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45846</v>
+        <v>44930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2391,7 +2386,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2434,7 +2429,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2444,14 +2439,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46112</v>
+        <v>45513</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2464,7 +2459,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2507,7 +2502,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2517,14 +2512,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45694</v>
+        <v>46062</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2537,7 +2532,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>5.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2580,7 +2575,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2594,10 +2589,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44928</v>
+        <v>45042</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2610,7 +2605,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2653,7 +2648,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2667,10 +2662,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45063</v>
+        <v>46112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2683,7 +2678,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2726,7 +2721,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2740,10 +2735,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45099</v>
+        <v>45327</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2756,7 +2751,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2799,7 +2794,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2809,14 +2804,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45327</v>
+        <v>45694</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2829,7 +2824,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2867,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,10 +2881,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45042</v>
+        <v>45589</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2945,7 +2940,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 53131-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2959,10 +2954,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46198</v>
+        <v>44468</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2975,7 +2970,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3018,7 +3013,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53131-2021</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3032,10 +3027,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44468</v>
+        <v>46198</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3048,7 +3043,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3091,7 +3086,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3105,10 +3100,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46223</v>
+        <v>45327</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3116,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3164,7 +3159,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3178,10 +3173,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45327</v>
+        <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3237,7 +3232,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3251,10 +3246,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45762</v>
+        <v>45722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3266,8 +3261,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3310,7 +3310,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45327</v>
+        <v>45846</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3400,7 +3400,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>45307</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45762</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45099</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44573</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>44928</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>45063</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>44930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>45513</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>46062</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45042</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>46112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>45327</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>45694</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45589</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>44468</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>46198</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>45327</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>45722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>45846</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>45307</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45762</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45099</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44573</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>44928</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45063</v>
+        <v>46062</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44930</v>
+        <v>45063</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2429,7 +2429,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2439,14 +2439,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45513</v>
+        <v>44930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2512,14 +2512,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46062</v>
+        <v>45513</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2575,7 +2575,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45042</v>
+        <v>46112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46112</v>
+        <v>45042</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>45327</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2804,14 +2804,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45694</v>
+        <v>46198</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2867,7 +2867,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2877,14 +2877,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45589</v>
+        <v>45694</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2940,7 +2940,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 53131-2021</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44468</v>
+        <v>45589</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46198</v>
+        <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 53131-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3100,10 +3100,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45327</v>
+        <v>44468</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3159,7 +3159,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46223</v>
+        <v>45327</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3249,7 +3249,7 @@
         <v>45722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>45846</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45762</v>
+        <v>45307</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1309,50 +1309,46 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1366,10 +1362,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45762</v>
+        <v>44929</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1385,10 +1381,10 @@
         <v>2.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1422,42 +1418,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1471,10 +1467,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44929</v>
+        <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1483,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1527,42 +1523,46 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45307</v>
+        <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1628,39 +1628,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1789,7 +1789,7 @@
         <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1855,14 +1855,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45762</v>
+        <v>45694</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45099</v>
+        <v>44928</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44957</v>
+        <v>45063</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2064,7 +2064,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44573</v>
+        <v>44957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44928</v>
+        <v>44573</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2227,7 +2227,7 @@
         <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46062</v>
+        <v>45099</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2366,14 +2366,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45063</v>
+        <v>45513</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2429,7 +2429,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44930</v>
+        <v>45327</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2502,7 +2502,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2512,14 +2512,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45513</v>
+        <v>44930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46112</v>
+        <v>45589</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45042</v>
+        <v>45722</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2677,8 +2677,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2721,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2735,10 +2740,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45327</v>
+        <v>45042</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2751,7 +2756,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2794,7 +2799,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2808,10 +2813,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46198</v>
+        <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2867,7 +2872,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 53131-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2877,14 +2882,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45694</v>
+        <v>44468</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2897,7 +2902,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2940,7 +2945,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2954,10 +2959,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45589</v>
+        <v>46062</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2970,7 +2975,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3013,7 +3018,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3027,10 +3032,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46223</v>
+        <v>45846</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3043,7 +3048,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3086,7 +3091,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53131-2021</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3100,10 +3105,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44468</v>
+        <v>46112</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3116,7 +3121,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3159,7 +3164,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3176,7 +3181,7 @@
         <v>45327</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3189,7 +3194,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3232,7 +3237,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3246,10 +3251,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45722</v>
+        <v>45762</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3261,13 +3266,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3310,7 +3310,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45846</v>
+        <v>46198</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3400,7 +3400,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45307</v>
+        <v>45762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1309,39 +1309,43 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
@@ -1365,7 +1369,7 @@
         <v>44929</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1453,7 +1457,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1470,7 +1474,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1483,13 +1487,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1523,46 +1527,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45762</v>
+        <v>45307</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1628,39 +1628,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1789,7 +1789,7 @@
         <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1855,14 +1855,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45694</v>
+        <v>45762</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44928</v>
+        <v>45099</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45063</v>
+        <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2064,7 +2064,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44957</v>
+        <v>44573</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44573</v>
+        <v>44928</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2227,7 +2227,7 @@
         <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45099</v>
+        <v>46062</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2366,14 +2366,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45513</v>
+        <v>45063</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2429,7 +2429,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45327</v>
+        <v>44930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2502,7 +2502,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2512,14 +2512,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44930</v>
+        <v>45513</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45589</v>
+        <v>46112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45722</v>
+        <v>45042</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2677,13 +2677,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2726,7 +2721,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2740,10 +2735,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45042</v>
+        <v>45327</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2756,7 +2751,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2799,7 +2794,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2809,14 +2804,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46223</v>
+        <v>45694</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2829,7 +2824,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2867,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 53131-2021</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,10 +2881,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44468</v>
+        <v>45589</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2902,7 +2897,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2945,7 +2940,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2959,10 +2954,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46062</v>
+        <v>46198</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2975,7 +2970,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3018,7 +3013,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 53131-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3032,10 +3027,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45846</v>
+        <v>44468</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3091,7 +3086,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3105,10 +3100,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46112</v>
+        <v>45327</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3116,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3164,7 +3159,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3178,10 +3173,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45327</v>
+        <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3237,7 +3232,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3251,10 +3246,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45762</v>
+        <v>45722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3266,8 +3261,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3310,7 +3310,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46198</v>
+        <v>45846</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3400,7 +3400,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45762</v>
+        <v>44929</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1313,46 +1313,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1362,14 +1358,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44929</v>
+        <v>45307</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1382,7 +1378,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1418,7 +1414,7 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
@@ -1426,38 +1422,38 @@
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1474,7 +1470,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,13 +1483,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1527,42 +1523,46 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45307</v>
+        <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1628,39 +1628,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45327</v>
+        <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45762</v>
+        <v>44573</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45099</v>
+        <v>45327</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44957</v>
+        <v>45513</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2064,7 +2064,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44573</v>
+        <v>46062</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>5.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44928</v>
+        <v>44930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45327</v>
+        <v>45589</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46062</v>
+        <v>46112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2366,14 +2366,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45063</v>
+        <v>45694</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2429,7 +2429,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44930</v>
+        <v>45722</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2458,8 +2458,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2502,7 +2507,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2512,14 +2517,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45513</v>
+        <v>44928</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2575,7 +2580,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2589,10 +2594,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46112</v>
+        <v>45063</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2605,7 +2610,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2648,7 +2653,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2662,10 +2667,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45042</v>
+        <v>45846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2678,7 +2683,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2721,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2735,10 +2740,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45327</v>
+        <v>45099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2751,7 +2756,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2794,7 +2799,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2804,14 +2809,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45694</v>
+        <v>45327</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2824,7 +2829,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2867,7 +2872,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2881,10 +2886,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45589</v>
+        <v>46198</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2897,7 +2902,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2940,7 +2945,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2954,10 +2959,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46198</v>
+        <v>45042</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2970,7 +2975,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3030,7 +3035,7 @@
         <v>44468</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3086,7 +3091,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3100,10 +3105,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45327</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3116,7 +3121,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3159,7 +3164,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3173,10 +3178,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46223</v>
+        <v>45327</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3232,7 +3237,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3246,10 +3251,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45722</v>
+        <v>45762</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3261,13 +3266,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3310,7 +3310,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45846</v>
+        <v>45327</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3400,7 +3400,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>44929</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>45307</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>44573</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45327</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>45513</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>46062</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>44930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>45589</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>46112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45694</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>45722</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>44928</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>45063</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>45846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45327</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>46198</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>45042</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>44468</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>45327</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>45762</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>45327</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>44929</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>45307</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>44573</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45327</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>45513</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>46062</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>44930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>45589</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>46112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45694</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>45722</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>44928</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>45063</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>45846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45327</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>46198</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>45042</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>44468</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>45327</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>45762</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>45327</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>44929</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1358,14 +1358,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45307</v>
+        <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1414,46 +1414,50 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1470,7 +1474,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1483,13 +1487,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1523,46 +1527,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45762</v>
+        <v>45307</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1628,39 +1628,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44957</v>
+        <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44573</v>
+        <v>45762</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45327</v>
+        <v>45722</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1947,8 +1947,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1991,7 +1996,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2001,14 +2006,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45513</v>
+        <v>45846</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2021,7 +2026,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2064,7 +2069,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2078,10 +2083,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46062</v>
+        <v>45099</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2094,7 +2099,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2137,7 +2142,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2151,10 +2156,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44930</v>
+        <v>44957</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2167,7 +2172,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2210,7 +2215,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2224,10 +2229,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45589</v>
+        <v>44573</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2240,7 +2245,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2283,7 +2288,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2297,10 +2302,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46112</v>
+        <v>46062</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2313,7 +2318,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2356,7 +2361,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2366,14 +2371,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45694</v>
+        <v>46112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2386,7 +2391,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2429,7 +2434,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2443,10 +2448,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45722</v>
+        <v>44928</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2458,13 +2463,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44928</v>
+        <v>45327</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2597,7 +2597,7 @@
         <v>45063</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45846</v>
+        <v>44930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45099</v>
+        <v>45513</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45327</v>
+        <v>45042</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46198</v>
+        <v>45327</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2955,14 +2955,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45042</v>
+        <v>45694</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53131-2021</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44468</v>
+        <v>45589</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 53131-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46223</v>
+        <v>44468</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3181,7 +3181,7 @@
         <v>45327</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45762</v>
+        <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3310,7 +3310,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45327</v>
+        <v>46198</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3400,7 +3400,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE35"/>
+  <dimension ref="A1:AE34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44929</v>
+        <v>45307</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
@@ -1317,38 +1317,38 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45762</v>
+        <v>44929</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1418,46 +1418,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1474,7 +1470,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,13 +1483,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1527,42 +1523,46 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45307</v>
+        <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1628,39 +1628,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45327</v>
+        <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45762</v>
+        <v>44573</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45722</v>
+        <v>45327</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1947,13 +1947,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1996,7 +1991,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2010,10 +2005,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45846</v>
+        <v>45722</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2025,8 +2020,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2069,7 +2069,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2079,14 +2079,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45099</v>
+        <v>45513</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2142,7 +2142,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44957</v>
+        <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44573</v>
+        <v>44930</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2288,7 +2288,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46062</v>
+        <v>45589</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46112</v>
+        <v>46062</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2444,14 +2444,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44928</v>
+        <v>45694</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45327</v>
+        <v>46112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2580,7 +2580,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45063</v>
+        <v>44928</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2653,7 +2653,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44930</v>
+        <v>45063</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45513</v>
+        <v>45099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45042</v>
+        <v>45327</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45327</v>
+        <v>45042</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2955,14 +2955,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45694</v>
+        <v>45327</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45589</v>
+        <v>45762</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53131-2021</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44468</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
         <v>45327</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46223</v>
+        <v>46198</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3307,27 +3307,27 @@
       </c>
       <c r="V33" s="2" t="inlineStr"/>
     </row>
-    <row r="34" ht="15" customHeight="1">
+    <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>S 4386-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46198</v>
+        <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>21.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3379,79 +3379,6 @@
         <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>S 4386-2022</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>44783</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>BÅSTAD</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 2943-2023</t>
+          <t>A 11517-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -933,14 +933,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44945</v>
+        <v>45372</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -953,16 +953,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>11.3</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -977,7 +977,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -989,148 +989,148 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Tvåblad
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 11517-2024 artfynd.xlsx", "A 11517-2024")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 11517-2024 karta.png", "A 11517-2024")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 11517-2024 georefererad karta.tif", "A 11517-2024")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 11517-2024 FSC-klagomål.docx", "A 11517-2024")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 11517-2024 FSC-klagomål mail.docx", "A 11517-2024")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 11517-2024 tillsynsbegäran.docx", "A 11517-2024")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 11517-2024 tillsynsbegäran mail.docx", "A 11517-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 2943-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>44945</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BÅSTAD</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Sårläka
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 2943-2023 artfynd.xlsx", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 2943-2023 karta.png", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 2943-2023 georefererad karta.tif", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 2943-2023 FSC-klagomål.docx", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 2943-2023 FSC-klagomål mail.docx", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 2943-2023 tillsynsbegäran.docx", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 2943-2023 tillsynsbegäran mail.docx", "A 2943-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 11517-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45372</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BÅSTAD</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Tvåblad
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 11517-2024 artfynd.xlsx", "A 11517-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 11517-2024 karta.png", "A 11517-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 11517-2024 georefererad karta.tif", "A 11517-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 11517-2024 FSC-klagomål.docx", "A 11517-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 11517-2024 FSC-klagomål mail.docx", "A 11517-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 11517-2024 tillsynsbegäran.docx", "A 11517-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 11517-2024 tillsynsbegäran mail.docx", "A 11517-2024")</f>
         <v/>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45307</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>44929</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44957</v>
+        <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44573</v>
+        <v>45589</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45327</v>
+        <v>44957</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45722</v>
+        <v>45327</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2020,13 +2020,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2069,7 +2064,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2079,14 +2074,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45513</v>
+        <v>45063</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2099,7 +2094,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2142,7 +2137,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2156,10 +2151,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45846</v>
+        <v>44573</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2172,7 +2167,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2215,7 +2210,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2229,10 +2224,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44930</v>
+        <v>45762</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2245,7 +2240,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2288,7 +2283,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2302,10 +2297,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45589</v>
+        <v>44930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2318,7 +2313,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2361,7 +2356,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2371,14 +2366,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46062</v>
+        <v>45513</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2391,7 +2386,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2434,7 +2429,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2444,14 +2439,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45694</v>
+        <v>45327</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2464,7 +2459,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2507,7 +2502,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2521,10 +2516,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46112</v>
+        <v>45042</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2580,7 +2575,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2594,10 +2589,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44928</v>
+        <v>45327</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2610,7 +2605,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2653,7 +2648,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2667,10 +2662,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45063</v>
+        <v>45722</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2682,8 +2677,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45099</v>
+        <v>45694</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45327</v>
+        <v>45846</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45042</v>
+        <v>44928</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45327</v>
+        <v>45099</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45762</v>
+        <v>46062</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46223</v>
+        <v>46112</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45327</v>
+        <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
         <v>46198</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 11517-2024</t>
+          <t>A 2943-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -933,14 +933,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45372</v>
+        <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -953,16 +953,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>11.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -977,7 +977,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -989,148 +989,148 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sårläka
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 2943-2023 artfynd.xlsx", "A 2943-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 2943-2023 karta.png", "A 2943-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 2943-2023 georefererad karta.tif", "A 2943-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 2943-2023 FSC-klagomål.docx", "A 2943-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 2943-2023 FSC-klagomål mail.docx", "A 2943-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 2943-2023 tillsynsbegäran.docx", "A 2943-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 2943-2023 tillsynsbegäran mail.docx", "A 2943-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 11517-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45372</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BÅSTAD</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Tvåblad
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 11517-2024 artfynd.xlsx", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 11517-2024 karta.png", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 11517-2024 georefererad karta.tif", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 11517-2024 FSC-klagomål.docx", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 11517-2024 FSC-klagomål mail.docx", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 11517-2024 tillsynsbegäran.docx", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 11517-2024 tillsynsbegäran mail.docx", "A 11517-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 2943-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44945</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BÅSTAD</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sårläka
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 2943-2023 artfynd.xlsx", "A 2943-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 2943-2023 karta.png", "A 2943-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 2943-2023 georefererad karta.tif", "A 2943-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 2943-2023 FSC-klagomål.docx", "A 2943-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 2943-2023 FSC-klagomål mail.docx", "A 2943-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 2943-2023 tillsynsbegäran.docx", "A 2943-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 2943-2023 tillsynsbegäran mail.docx", "A 2943-2023")</f>
         <v/>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45307</v>
+        <v>44929</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
@@ -1317,38 +1317,38 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1358,14 +1358,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44929</v>
+        <v>45307</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1414,7 +1414,7 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
@@ -1422,31 +1422,31 @@
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45327</v>
+        <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45589</v>
+        <v>44573</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44957</v>
+        <v>45327</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45327</v>
+        <v>46062</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2064,7 +2064,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2074,14 +2074,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45063</v>
+        <v>45513</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44573</v>
+        <v>44930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2210,7 +2210,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45762</v>
+        <v>45589</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44930</v>
+        <v>46112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2366,14 +2366,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45513</v>
+        <v>45722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2385,8 +2385,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2429,7 +2434,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2443,10 +2448,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45327</v>
+        <v>45846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2459,7 +2464,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2502,7 +2507,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2512,14 +2517,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45042</v>
+        <v>45694</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2532,7 +2537,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2575,7 +2580,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2589,10 +2594,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45327</v>
+        <v>44928</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2605,7 +2610,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2648,7 +2653,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2662,10 +2667,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45722</v>
+        <v>45063</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2677,13 +2682,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45694</v>
+        <v>45099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45846</v>
+        <v>45327</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44928</v>
+        <v>45042</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45099</v>
+        <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46062</v>
+        <v>45327</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46112</v>
+        <v>46198</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46223</v>
+        <v>45762</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46198</v>
+        <v>45327</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>44929</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1358,14 +1358,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45307</v>
+        <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1414,46 +1414,50 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1470,7 +1474,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1483,13 +1487,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1523,46 +1527,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45762</v>
+        <v>45307</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1628,39 +1628,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44957</v>
+        <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44573</v>
+        <v>45762</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45327</v>
+        <v>45099</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2008,7 +2008,7 @@
         <v>46062</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2074,14 +2074,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45513</v>
+        <v>44957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44930</v>
+        <v>46112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2210,7 +2210,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45589</v>
+        <v>45722</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2239,8 +2239,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2283,7 +2288,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2297,10 +2302,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46112</v>
+        <v>44573</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2313,7 +2318,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2356,7 +2361,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2370,10 +2375,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45722</v>
+        <v>45846</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2385,13 +2390,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45846</v>
+        <v>44928</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2517,14 +2517,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45694</v>
+        <v>45327</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2580,7 +2580,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44928</v>
+        <v>45063</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2653,7 +2653,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45063</v>
+        <v>44930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45099</v>
+        <v>45513</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45327</v>
+        <v>45042</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45042</v>
+        <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46223</v>
+        <v>45327</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45327</v>
+        <v>46198</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3101,14 +3101,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46198</v>
+        <v>45694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45762</v>
+        <v>45589</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
         <v>45327</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>44929</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>45307</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45762</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45099</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>46062</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>46112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>45722</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>44573</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45846</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>44928</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45327</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>45063</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>44930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45513</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45042</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>45327</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>46198</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>45694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>45589</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>45327</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>44929</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>45307</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45762</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45099</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>46062</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>46112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>45722</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>44573</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45846</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>44928</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45327</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>45063</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>44930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45513</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45042</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>45327</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>46198</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>45694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>45589</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>45327</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44929</v>
+        <v>45307</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
@@ -1317,38 +1317,38 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45762</v>
+        <v>44929</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1418,46 +1418,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1474,7 +1470,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,13 +1483,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1527,42 +1523,46 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45307</v>
+        <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1628,39 +1628,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45327</v>
+        <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45762</v>
+        <v>44573</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45099</v>
+        <v>45327</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46062</v>
+        <v>45722</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2020,8 +2020,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>5.9</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2064,7 +2069,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2074,14 +2079,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44957</v>
+        <v>45513</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2094,7 +2099,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2137,7 +2142,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2151,10 +2156,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46112</v>
+        <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2167,7 +2172,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2210,7 +2215,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2224,10 +2229,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45722</v>
+        <v>44930</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2239,13 +2244,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2288,7 +2288,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44573</v>
+        <v>45589</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45846</v>
+        <v>46062</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44928</v>
+        <v>46112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2517,14 +2517,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45327</v>
+        <v>45694</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2580,7 +2580,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45063</v>
+        <v>44928</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2653,7 +2653,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44930</v>
+        <v>45063</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45513</v>
+        <v>45099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45042</v>
+        <v>45327</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46223</v>
+        <v>45042</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2962,7 +2962,7 @@
         <v>45327</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46198</v>
+        <v>45762</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3101,14 +3101,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45694</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45589</v>
+        <v>46198</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
         <v>45327</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45307</v>
+        <v>44929</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
@@ -1317,38 +1317,38 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44929</v>
+        <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1418,42 +1418,46 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1470,7 +1474,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1483,13 +1487,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1523,46 +1527,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45762</v>
+        <v>45307</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1628,39 +1628,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44957</v>
+        <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44573</v>
+        <v>45762</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45327</v>
+        <v>45099</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2008,7 +2008,7 @@
         <v>45722</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2079,14 +2079,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45513</v>
+        <v>46062</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2142,7 +2142,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45846</v>
+        <v>44957</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44930</v>
+        <v>45846</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2288,7 +2288,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45589</v>
+        <v>46112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46062</v>
+        <v>44573</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46112</v>
+        <v>44928</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2517,14 +2517,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45694</v>
+        <v>45327</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2580,7 +2580,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44928</v>
+        <v>45063</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2653,7 +2653,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45063</v>
+        <v>44930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45099</v>
+        <v>45513</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45327</v>
+        <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45042</v>
+        <v>46198</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45327</v>
+        <v>45042</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45762</v>
+        <v>45327</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3101,14 +3101,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46223</v>
+        <v>45694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46198</v>
+        <v>45589</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
         <v>45327</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44929</v>
+        <v>45307</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
@@ -1317,31 +1317,31 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45307</v>
+        <v>44929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -1636,31 +1636,31 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1782,14 +1782,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45327</v>
+        <v>45694</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45762</v>
+        <v>45327</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45099</v>
+        <v>44928</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45722</v>
+        <v>45063</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2020,13 +2020,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2069,7 +2064,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2083,10 +2078,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46062</v>
+        <v>44957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2099,7 +2094,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2142,7 +2137,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2156,10 +2151,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44957</v>
+        <v>45722</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,8 +2166,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45846</v>
+        <v>44573</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2288,7 +2288,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46112</v>
+        <v>45099</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44573</v>
+        <v>45327</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44928</v>
+        <v>45846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2524,7 +2524,7 @@
         <v>45327</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2580,7 +2580,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2590,14 +2590,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45063</v>
+        <v>45513</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2670,7 +2670,7 @@
         <v>44930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45513</v>
+        <v>45589</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46223</v>
+        <v>45042</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46198</v>
+        <v>46062</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>5.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45042</v>
+        <v>46112</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>45327</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3101,14 +3101,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45694</v>
+        <v>45762</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45589</v>
+        <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45327</v>
+        <v>46198</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45307</v>
+        <v>45762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1309,46 +1309,50 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1362,10 +1366,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45762</v>
+        <v>44929</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1382,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1418,46 +1422,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1467,14 +1467,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45762</v>
+        <v>45307</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,13 +1487,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1523,46 +1523,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44929</v>
+        <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1595,10 +1595,10 @@
         <v>2.5</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1632,35 +1632,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1782,14 +1782,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45694</v>
+        <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45327</v>
+        <v>45762</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44928</v>
+        <v>45099</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45063</v>
+        <v>45846</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2081,7 +2081,7 @@
         <v>44957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45722</v>
+        <v>44573</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2166,13 +2166,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2215,7 +2210,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2229,10 +2224,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44573</v>
+        <v>46112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2245,7 +2240,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2288,7 +2283,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2302,10 +2297,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45099</v>
+        <v>44928</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2318,7 +2313,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2378,7 +2373,7 @@
         <v>45327</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2434,7 +2429,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2448,10 +2443,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45846</v>
+        <v>46062</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2464,7 +2459,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2507,7 +2502,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2521,10 +2516,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45327</v>
+        <v>45063</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2537,7 +2532,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2580,7 +2575,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2590,14 +2585,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45513</v>
+        <v>44930</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2653,7 +2648,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2663,14 +2658,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44930</v>
+        <v>45513</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2726,7 +2721,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2740,10 +2735,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45589</v>
+        <v>45042</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2799,7 +2794,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2813,10 +2808,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45042</v>
+        <v>45327</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2829,7 +2824,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2867,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2882,14 +2877,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46062</v>
+        <v>45694</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2902,7 +2897,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.9</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2945,7 +2940,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2959,10 +2954,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46112</v>
+        <v>45589</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3018,7 +3013,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3035,7 +3030,7 @@
         <v>45327</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3048,7 +3043,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3091,7 +3086,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3105,10 +3100,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45762</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3116,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3164,7 +3159,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3178,10 +3173,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46223</v>
+        <v>46198</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3237,7 +3232,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3251,10 +3246,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46198</v>
+        <v>45722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3266,8 +3261,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45762</v>
+        <v>45307</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1309,50 +1309,46 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1366,10 +1362,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44929</v>
+        <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1382,7 +1378,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1422,42 +1418,46 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1467,14 +1467,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45307</v>
+        <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1523,7 +1523,7 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
@@ -1531,31 +1531,31 @@
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
         <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45327</v>
+        <v>44928</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45762</v>
+        <v>45063</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45099</v>
+        <v>45762</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45846</v>
+        <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2064,7 +2064,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44957</v>
+        <v>44573</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44573</v>
+        <v>45327</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2210,7 +2210,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46112</v>
+        <v>45099</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44928</v>
+        <v>45327</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2366,14 +2366,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45327</v>
+        <v>45513</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2429,7 +2429,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46062</v>
+        <v>45327</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2502,7 +2502,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45063</v>
+        <v>44930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2575,7 +2575,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44930</v>
+        <v>45589</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2648,7 +2648,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2658,14 +2658,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45513</v>
+        <v>45722</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2677,8 +2677,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2721,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2735,10 +2740,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45042</v>
+        <v>45846</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2751,7 +2756,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2794,7 +2799,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2804,14 +2809,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45327</v>
+        <v>45694</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2824,7 +2829,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2867,7 +2872,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2877,14 +2882,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45694</v>
+        <v>45042</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2897,7 +2902,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2940,7 +2945,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2954,10 +2959,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45589</v>
+        <v>46112</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3013,7 +3018,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3030,7 +3035,7 @@
         <v>45327</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3043,7 +3048,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3086,7 +3091,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3100,10 +3105,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46223</v>
+        <v>46062</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3116,7 +3121,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>5.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3176,7 +3181,7 @@
         <v>46198</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3232,7 +3237,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3246,10 +3251,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45722</v>
+        <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3261,13 +3266,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45307</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>44928</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45063</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45762</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44573</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45327</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>45099</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>45327</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45513</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>45327</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>44930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45589</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45722</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45846</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45694</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>45042</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46112</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>45327</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>46062</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>46198</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45307</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>44928</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45063</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45762</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44573</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45327</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>45099</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>45327</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45513</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>45327</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>44930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45589</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45722</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45846</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45694</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>45042</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46112</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>45327</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>46062</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>46198</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45307</v>
+        <v>45762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1309,46 +1309,46 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45762</v>
+        <v>44929</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1418,46 +1418,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1471,10 +1467,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44929</v>
+        <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1487,7 +1483,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1527,42 +1523,46 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45762</v>
+        <v>45307</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1628,39 +1628,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44928</v>
+        <v>45589</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45063</v>
+        <v>45327</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45762</v>
+        <v>45327</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44957</v>
+        <v>45762</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2064,7 +2064,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44573</v>
+        <v>45722</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2093,8 +2093,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2137,7 +2142,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2151,10 +2156,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45327</v>
+        <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2167,7 +2172,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2210,7 +2215,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2224,10 +2229,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45099</v>
+        <v>46198</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2240,7 +2245,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2283,7 +2288,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2297,10 +2302,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45327</v>
+        <v>46062</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2313,7 +2318,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>5.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2356,7 +2361,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2366,14 +2371,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45513</v>
+        <v>46112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2386,7 +2391,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2429,7 +2434,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2443,10 +2448,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45327</v>
+        <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2459,7 +2464,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2502,7 +2507,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2516,10 +2521,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44930</v>
+        <v>45099</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2532,7 +2537,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2575,7 +2580,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2589,10 +2594,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45589</v>
+        <v>44957</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2605,7 +2610,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2648,7 +2653,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2662,10 +2667,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45722</v>
+        <v>44573</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2677,13 +2682,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45846</v>
+        <v>44928</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2809,14 +2809,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45694</v>
+        <v>45327</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45042</v>
+        <v>45063</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46112</v>
+        <v>44930</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3028,14 +3028,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45327</v>
+        <v>45513</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46062</v>
+        <v>45042</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46198</v>
+        <v>45327</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3247,14 +3247,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46223</v>
+        <v>45694</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45762</v>
+        <v>45307</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1309,39 +1309,39 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         <v>44929</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45307</v>
+        <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1628,39 +1628,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45589</v>
+        <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45327</v>
+        <v>44573</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1935,7 +1935,7 @@
         <v>45327</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45762</v>
+        <v>45722</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2020,8 +2020,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2064,7 +2069,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2074,14 +2079,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45722</v>
+        <v>45513</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2093,13 +2098,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46198</v>
+        <v>44930</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2288,7 +2288,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46062</v>
+        <v>45589</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46112</v>
+        <v>46062</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2444,14 +2444,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46223</v>
+        <v>45694</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45099</v>
+        <v>46112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2580,7 +2580,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44957</v>
+        <v>44928</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2653,7 +2653,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44573</v>
+        <v>45063</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44928</v>
+        <v>45099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2816,7 +2816,7 @@
         <v>45327</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45063</v>
+        <v>45042</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44930</v>
+        <v>45327</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3028,14 +3028,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45513</v>
+        <v>45762</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45042</v>
+        <v>46198</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3181,7 +3181,7 @@
         <v>45327</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3247,14 +3247,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45694</v>
+        <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45307</v>
+        <v>45762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1309,39 +1309,43 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
@@ -1365,7 +1369,7 @@
         <v>44929</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1453,7 +1457,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1470,7 +1474,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1483,13 +1487,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1523,46 +1527,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45762</v>
+        <v>45307</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1628,39 +1628,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44957</v>
+        <v>45722</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1801,8 +1801,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1850,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1864,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44573</v>
+        <v>45327</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1880,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1923,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1937,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45327</v>
+        <v>45762</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1991,7 +1996,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2005,10 +2010,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45722</v>
+        <v>45846</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2020,13 +2025,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2069,7 +2069,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2079,14 +2079,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45513</v>
+        <v>46062</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2142,7 +2142,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45846</v>
+        <v>45099</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44930</v>
+        <v>46112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2288,7 +2288,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45589</v>
+        <v>44957</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46062</v>
+        <v>44573</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2444,14 +2444,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45694</v>
+        <v>44928</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46112</v>
+        <v>45327</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2580,7 +2580,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44928</v>
+        <v>45063</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2653,7 +2653,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45063</v>
+        <v>44930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45099</v>
+        <v>45513</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45327</v>
+        <v>45042</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45042</v>
+        <v>45327</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2955,14 +2955,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45327</v>
+        <v>45694</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45762</v>
+        <v>46198</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46198</v>
+        <v>45589</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45327</v>
+        <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46223</v>
+        <v>45327</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45762</v>
+        <v>45307</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1309,50 +1309,46 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1366,10 +1362,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44929</v>
+        <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1382,7 +1378,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1422,35 +1418,39 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45307</v>
+        <v>44929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -1636,31 +1636,31 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45722</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45327</v>
+        <v>44928</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45762</v>
+        <v>45063</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1996,7 +1996,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45846</v>
+        <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2069,7 +2069,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46062</v>
+        <v>45846</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2142,7 +2142,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45099</v>
+        <v>44573</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46112</v>
+        <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2288,7 +2288,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44957</v>
+        <v>45099</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2371,14 +2371,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44573</v>
+        <v>45513</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44928</v>
+        <v>46112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2524,7 +2524,7 @@
         <v>45327</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2580,7 +2580,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45063</v>
+        <v>44930</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2653,7 +2653,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44930</v>
+        <v>45589</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45513</v>
+        <v>45694</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2816,7 +2816,7 @@
         <v>45042</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>45327</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2955,14 +2955,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45694</v>
+        <v>45762</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
         <v>46198</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45589</v>
+        <v>45327</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45327</v>
+        <v>46062</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>5.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45307</v>
+        <v>45762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1309,46 +1309,50 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1365,7 +1369,7 @@
         <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1378,13 +1382,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1418,46 +1422,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45762</v>
+        <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>2.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1527,42 +1527,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44929</v>
+        <v>45307</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -1636,31 +1636,31 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45722</v>
+        <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1801,13 +1801,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1850,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1864,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44928</v>
+        <v>45762</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1880,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1923,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1937,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45063</v>
+        <v>45099</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1953,7 +1948,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2013,7 +2008,7 @@
         <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2069,7 +2064,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2083,10 +2078,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45846</v>
+        <v>44573</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2099,7 +2094,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2142,7 +2137,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2156,10 +2151,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44573</v>
+        <v>44928</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2172,7 +2167,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2232,7 +2227,7 @@
         <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2288,7 +2283,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2302,10 +2297,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45099</v>
+        <v>46062</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2318,7 +2313,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2361,7 +2356,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2371,14 +2366,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45513</v>
+        <v>45063</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2391,7 +2386,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2434,7 +2429,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2448,10 +2443,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46112</v>
+        <v>44930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2464,7 +2459,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2507,7 +2502,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2517,14 +2512,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45327</v>
+        <v>45513</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2537,7 +2532,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2580,7 +2575,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2594,10 +2589,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44930</v>
+        <v>46112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2610,7 +2605,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2653,7 +2648,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2667,10 +2662,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45589</v>
+        <v>45042</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2726,7 +2721,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2736,14 +2731,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45694</v>
+        <v>45327</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2756,7 +2751,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2799,7 +2794,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2809,14 +2804,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45042</v>
+        <v>45694</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2829,7 +2824,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2867,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,10 +2881,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45327</v>
+        <v>45589</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2902,7 +2897,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2945,7 +2940,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2959,10 +2954,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45762</v>
+        <v>46198</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2975,7 +2970,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3018,7 +3013,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3032,10 +3027,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46198</v>
+        <v>45327</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3048,7 +3043,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3091,7 +3086,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3105,10 +3100,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45327</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3121,7 +3116,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3164,7 +3159,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3178,10 +3173,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46223</v>
+        <v>45722</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3193,8 +3188,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46062</v>
+        <v>45846</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>45307</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45762</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45099</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44573</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>44928</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>46062</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45063</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>44930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>45513</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>46112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45042</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>45327</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>45694</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45589</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>46198</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>45327</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45722</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>45846</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>45307</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45762</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45099</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44573</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>44928</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>46062</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45063</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>44930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>45513</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>46112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45042</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>45327</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>45694</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45589</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>46198</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>45327</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45722</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>45846</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>44945</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>45209</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45762</v>
+        <v>45307</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1309,43 +1309,39 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
@@ -1369,7 +1365,7 @@
         <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1470,7 @@
         <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1562,7 +1558,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,14 +1568,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45307</v>
+        <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1592,7 +1588,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1628,39 +1624,43 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
         <v>45055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45327</v>
+        <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45762</v>
+        <v>44573</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45099</v>
+        <v>45327</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44957</v>
+        <v>45513</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2064,7 +2064,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44573</v>
+        <v>44930</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44928</v>
+        <v>45589</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2210,7 +2210,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2220,14 +2220,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45327</v>
+        <v>45694</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46062</v>
+        <v>44928</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2373,7 +2373,7 @@
         <v>45063</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44930</v>
+        <v>45099</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2502,7 +2502,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2512,14 +2512,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45513</v>
+        <v>45327</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2575,7 +2575,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46112</v>
+        <v>46062</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2648,7 +2648,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45042</v>
+        <v>46112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45327</v>
+        <v>45042</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2804,14 +2804,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45694</v>
+        <v>45327</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2867,7 +2867,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45589</v>
+        <v>45762</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2957,7 +2957,7 @@
         <v>46198</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>45327</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45722</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>45846</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE34"/>
+  <dimension ref="A1:AE35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,75 +815,188 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
+          <t>A 43546-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BÅSTAD</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Björktrast
+Nötkråka
+Talltita
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 43546-2026 artfynd.xlsx", "A 43546-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 43546-2026 karta.png", "A 43546-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 43546-2026 georefererad karta.tif", "A 43546-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 43546-2026 FSC-klagomål.docx", "A 43546-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 43546-2026 FSC-klagomål mail.docx", "A 43546-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 43546-2026 tillsynsbegäran.docx", "A 43546-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 43546-2026 tillsynsbegäran mail.docx", "A 43546-2026")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 43546-2026 prioriterade fågelarter.docx", "A 43546-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>A 38013-2022</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D5" s="1" t="n">
         <v>44811</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="E5" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>SKÅNE LÄN</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I5" t="n">
         <v>5.3</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>3</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R5" t="n">
         <v>1</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S5" t="n">
         <v>4</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T5" t="n">
         <v>4</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Blåmossa
@@ -891,359 +1004,253 @@
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 38013-2022 artfynd.xlsx", "A 38013-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 38013-2022 karta.png", "A 38013-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 38013-2022 georefererad karta.tif", "A 38013-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 38013-2022 FSC-klagomål.docx", "A 38013-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 38013-2022 FSC-klagomål mail.docx", "A 38013-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 38013-2022 tillsynsbegäran.docx", "A 38013-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 38013-2022 tillsynsbegäran mail.docx", "A 38013-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 2943-2023</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D6" s="1" t="n">
         <v>44945</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E6" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>SKÅNE LÄN</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I6" t="n">
         <v>11.3</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S6" t="n">
         <v>3</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>3</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Sårläka
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 2943-2023 artfynd.xlsx", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 2943-2023 karta.png", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 2943-2023 georefererad karta.tif", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 2943-2023 FSC-klagomål.docx", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 2943-2023 FSC-klagomål mail.docx", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 2943-2023 tillsynsbegäran.docx", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 2943-2023 tillsynsbegäran mail.docx", "A 2943-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 11517-2024</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>45372</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E7" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>SKÅNE LÄN</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>0.7</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>2</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R7" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S7" t="n">
         <v>3</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>3</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Tvåblad
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 11517-2024 artfynd.xlsx", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 11517-2024 karta.png", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 11517-2024 georefererad karta.tif", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 11517-2024 FSC-klagomål.docx", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 11517-2024 FSC-klagomål mail.docx", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 11517-2024 tillsynsbegäran.docx", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 11517-2024 tillsynsbegäran mail.docx", "A 11517-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 48974-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45209</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>BÅSTAD</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Gullpudra</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 48974-2023 artfynd.xlsx", "A 48974-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 48974-2023 karta.png", "A 48974-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 48974-2023 georefererad karta.tif", "A 48974-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 48974-2023 FSC-klagomål.docx", "A 48974-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 48974-2023 FSC-klagomål mail.docx", "A 48974-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 48974-2023 tillsynsbegäran.docx", "A 48974-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 48974-2023 tillsynsbegäran mail.docx", "A 48974-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 48974-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,14 +1260,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45307</v>
+        <v>45209</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1273,22 +1280,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1297,58 +1304,59 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Ask
+Gullpudra</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 48974-2023 artfynd.xlsx", "A 48974-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 48974-2023 karta.png", "A 48974-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 48974-2023 georefererad karta.tif", "A 48974-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 48974-2023 FSC-klagomål.docx", "A 48974-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 48974-2023 FSC-klagomål mail.docx", "A 48974-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 48974-2023 tillsynsbegäran.docx", "A 48974-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 48974-2023 tillsynsbegäran mail.docx", "A 48974-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1362,10 +1370,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45762</v>
+        <v>44929</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1381,10 +1389,10 @@
         <v>2.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1418,42 +1426,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1467,10 +1475,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44929</v>
+        <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1483,7 +1491,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1523,42 +1531,46 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1575,7 +1587,7 @@
         <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1588,13 +1600,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1628,63 +1640,59 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S 1528-2023</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45055</v>
+        <v>45307</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1697,13 +1705,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1733,63 +1741,63 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/S 1528-2023 artfynd.xlsx", "S 1528-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/S 1528-2023 karta.png", "S 1528-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/S 1528-2023 georefererad karta.tif", "S 1528-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/S 1528-2023 FSC-klagomål.docx", "S 1528-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/S 1528-2023 FSC-klagomål mail.docx", "S 1528-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/S 1528-2023 tillsynsbegäran.docx", "S 1528-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/S 1528-2023 tillsynsbegäran mail.docx", "S 1528-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>S 1528-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44957</v>
+        <v>45055</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1802,13 +1810,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1832,20 +1840,52 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/S 1528-2023 artfynd.xlsx", "S 1528-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/S 1528-2023 karta.png", "S 1528-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/S 1528-2023 georefererad karta.tif", "S 1528-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/S 1528-2023 FSC-klagomål.docx", "S 1528-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/S 1528-2023 FSC-klagomål mail.docx", "S 1528-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/S 1528-2023 tillsynsbegäran.docx", "S 1528-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/S 1528-2023 tillsynsbegäran mail.docx", "S 1528-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,10 +1899,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44573</v>
+        <v>45327</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1875,7 +1915,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1918,7 +1958,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1932,10 +1972,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45327</v>
+        <v>45762</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1991,7 +2031,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2001,14 +2041,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45513</v>
+        <v>45722</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2020,8 +2060,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2064,7 +2109,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2078,10 +2123,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44930</v>
+        <v>46062</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2094,7 +2139,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2137,7 +2182,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2151,10 +2196,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45589</v>
+        <v>45099</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2167,7 +2212,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2210,7 +2255,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2220,14 +2265,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45694</v>
+        <v>46112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2240,7 +2285,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2283,7 +2328,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2297,10 +2342,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44928</v>
+        <v>44957</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2313,7 +2358,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2356,7 +2401,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2370,10 +2415,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45063</v>
+        <v>44573</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2386,7 +2431,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2429,7 +2474,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2443,10 +2488,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45099</v>
+        <v>45846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2459,7 +2504,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2502,7 +2547,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2516,10 +2561,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45327</v>
+        <v>44928</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2532,7 +2577,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2575,7 +2620,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2589,10 +2634,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46062</v>
+        <v>45327</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2605,7 +2650,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.9</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2648,7 +2693,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2662,10 +2707,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46112</v>
+        <v>45063</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2678,7 +2723,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2721,7 +2766,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2735,10 +2780,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45042</v>
+        <v>44930</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2751,7 +2796,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2794,7 +2839,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2804,14 +2849,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45327</v>
+        <v>45513</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2824,7 +2869,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2867,7 +2912,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2881,10 +2926,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45762</v>
+        <v>46198</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2897,7 +2942,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2940,7 +2985,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2954,10 +2999,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46198</v>
+        <v>45042</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2970,7 +3015,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3013,7 +3058,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3030,7 +3075,7 @@
         <v>45327</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3043,7 +3088,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3103,7 +3148,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3159,7 +3204,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3169,14 +3214,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45722</v>
+        <v>45694</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3188,13 +3233,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3237,7 +3277,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3251,10 +3291,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45846</v>
+        <v>45589</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3267,7 +3307,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3307,78 +3347,151 @@
       </c>
       <c r="V33" s="2" t="inlineStr"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
+          <t>A 4493-2024</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>45327</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>BÅSTAD</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>S 4386-2022</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D34" s="1" t="n">
+      <c r="D35" s="1" t="n">
         <v>44783</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="E35" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>SKÅNE LÄN</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="I34" t="n">
+      <c r="I35" t="n">
         <v>21.9</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr"/>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46315</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44945</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>45372</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45209</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1366,14 +1366,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44929</v>
+        <v>45307</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
@@ -1430,38 +1430,38 @@
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45762</v>
+        <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1531,46 +1531,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1587,7 +1583,7 @@
         <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1600,13 +1596,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1640,42 +1636,46 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1685,14 +1685,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45307</v>
+        <v>45762</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1705,13 +1705,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1741,39 +1741,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
         <v>45055</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45327</v>
+        <v>44957</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45762</v>
+        <v>44573</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2031,7 +2031,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45722</v>
+        <v>45327</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2060,13 +2060,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2109,7 +2104,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2123,10 +2118,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46062</v>
+        <v>45722</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2138,8 +2133,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>5.9</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2182,7 +2182,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2192,14 +2192,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45099</v>
+        <v>45513</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2255,7 +2255,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46112</v>
+        <v>45846</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2328,7 +2328,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44957</v>
+        <v>44930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2401,7 +2401,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44573</v>
+        <v>45589</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2474,7 +2474,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45846</v>
+        <v>46062</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2547,7 +2547,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2557,14 +2557,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44928</v>
+        <v>45694</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45327</v>
+        <v>44928</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>45063</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44930</v>
+        <v>46112</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2849,14 +2849,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45513</v>
+        <v>45099</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46198</v>
+        <v>45327</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3002,7 +3002,7 @@
         <v>45042</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45327</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46223</v>
+        <v>45762</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3204,7 +3204,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3214,14 +3214,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45694</v>
+        <v>46198</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45589</v>
+        <v>45327</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3350,7 +3350,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45327</v>
+        <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46315</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44945</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>45372</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45209</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>45307</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44929</v>
+        <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1531,42 +1531,46 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1583,7 +1587,7 @@
         <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1596,13 +1600,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1636,46 +1640,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45762</v>
+        <v>44929</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
         <v>2.5</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1745,35 +1745,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
         <v>45055</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44957</v>
+        <v>45327</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44573</v>
+        <v>45762</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2031,7 +2031,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45327</v>
+        <v>45063</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2121,7 +2121,7 @@
         <v>45722</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2192,14 +2192,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45513</v>
+        <v>44930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2265,14 +2265,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45846</v>
+        <v>45513</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2328,7 +2328,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44930</v>
+        <v>45846</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2401,7 +2401,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45589</v>
+        <v>45042</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46062</v>
+        <v>45327</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2564,7 +2564,7 @@
         <v>45694</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44928</v>
+        <v>45589</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2693,7 +2693,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45063</v>
+        <v>45327</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2766,7 +2766,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46112</v>
+        <v>46062</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2856,7 +2856,7 @@
         <v>45099</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45327</v>
+        <v>46112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2985,7 +2985,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45042</v>
+        <v>44957</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3058,7 +3058,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45327</v>
+        <v>44573</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3131,7 +3131,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45762</v>
+        <v>46198</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3204,7 +3204,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46198</v>
+        <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45327</v>
+        <v>44928</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3350,7 +3350,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46223</v>
+        <v>45327</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46315</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44945</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>45372</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45209</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1366,14 +1366,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45307</v>
+        <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1386,13 +1386,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1422,46 +1422,46 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45762</v>
+        <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1531,46 +1531,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1587,7 +1583,7 @@
         <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1600,13 +1596,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1640,42 +1636,46 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1685,14 +1685,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44929</v>
+        <v>45307</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
@@ -1749,31 +1749,31 @@
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
         <v>45055</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1902,7 +1902,7 @@
         <v>45327</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45762</v>
+        <v>44957</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2031,7 +2031,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45063</v>
+        <v>45762</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2104,7 +2104,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45722</v>
+        <v>45327</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2131,11 +2131,6 @@
       <c r="G17" t="inlineStr">
         <is>
           <t>BÅSTAD</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -2182,7 +2177,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2196,10 +2191,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44930</v>
+        <v>46198</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2212,7 +2207,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2255,7 +2250,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2265,14 +2260,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45513</v>
+        <v>45722</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2284,8 +2279,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2328,7 +2328,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45846</v>
+        <v>46062</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2401,7 +2401,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45042</v>
+        <v>45846</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2474,7 +2474,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45327</v>
+        <v>46112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2547,7 +2547,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2557,14 +2557,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45694</v>
+        <v>44573</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45589</v>
+        <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2693,7 +2693,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2710,7 +2710,7 @@
         <v>45327</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2766,7 +2766,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2776,14 +2776,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46062</v>
+        <v>45513</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45099</v>
+        <v>44930</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46112</v>
+        <v>45589</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2995,14 +2995,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44957</v>
+        <v>45694</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3058,7 +3058,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44573</v>
+        <v>44928</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3131,7 +3131,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46198</v>
+        <v>45063</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3204,7 +3204,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46223</v>
+        <v>45099</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44928</v>
+        <v>45327</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3350,7 +3350,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45327</v>
+        <v>45042</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46315</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44945</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>45372</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45209</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45307</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>45055</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>45327</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>44957</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>45762</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>45327</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>46198</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>45722</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>46062</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45846</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>46112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>44573</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>45327</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>45513</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>44930</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>45589</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>45694</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>44928</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>45063</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45099</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>45327</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>45042</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46315</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44945</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>45372</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45209</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>45762</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45307</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>45055</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>45327</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>44957</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>45762</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>45327</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>46198</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>45722</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>46062</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45846</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>46112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>44573</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>45327</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>45513</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>44930</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>45589</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>45694</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>44928</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>45063</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45099</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>45327</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>45042</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46315</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44945</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>45372</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45209</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45762</v>
+        <v>44929</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         <v>2.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1426,42 +1426,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44929</v>
+        <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1531,42 +1531,46 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1583,7 +1587,7 @@
         <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1596,13 +1600,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1636,39 +1640,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
         <v>45307</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>45055</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45327</v>
+        <v>45589</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44957</v>
+        <v>45327</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         <v>45762</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>45327</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46198</v>
+        <v>45099</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2267,7 +2267,7 @@
         <v>45722</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46062</v>
+        <v>44957</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>45846</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46112</v>
+        <v>44573</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2547,7 +2547,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44573</v>
+        <v>46062</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>5.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46223</v>
+        <v>46112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2693,7 +2693,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45327</v>
+        <v>44928</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2766,7 +2766,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2776,14 +2776,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45513</v>
+        <v>45327</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44930</v>
+        <v>46198</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45589</v>
+        <v>45063</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2985,7 +2985,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2995,14 +2995,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45694</v>
+        <v>44930</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3058,7 +3058,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3068,14 +3068,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44928</v>
+        <v>45513</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45063</v>
+        <v>45042</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3204,7 +3204,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45099</v>
+        <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3294,7 +3294,7 @@
         <v>45327</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3350,7 +3350,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3360,14 +3360,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45042</v>
+        <v>45694</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46315</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44945</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>45372</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45209</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1366,14 +1366,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44929</v>
+        <v>45307</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
@@ -1430,38 +1430,38 @@
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45762</v>
+        <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1531,46 +1531,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1587,7 +1583,7 @@
         <v>45762</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1600,13 +1596,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1640,42 +1636,46 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1685,14 +1685,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45307</v>
+        <v>45762</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1705,13 +1705,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1741,39 +1741,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
         <v>45055</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45589</v>
+        <v>44957</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1968,14 +1968,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45327</v>
+        <v>45694</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2031,7 +2031,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45762</v>
+        <v>44928</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2104,7 +2104,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45327</v>
+        <v>45063</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2177,7 +2177,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45099</v>
+        <v>44573</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45722</v>
+        <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2279,13 +2279,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2328,7 +2323,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2338,14 +2333,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44957</v>
+        <v>45513</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2358,7 +2353,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2401,7 +2396,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2415,10 +2410,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45846</v>
+        <v>45099</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2431,7 +2426,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2474,7 +2469,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2488,10 +2483,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44573</v>
+        <v>44930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2504,7 +2499,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2547,7 +2542,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2561,10 +2556,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46062</v>
+        <v>45589</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2577,7 +2572,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2620,7 +2615,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2634,10 +2629,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46112</v>
+        <v>45327</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2650,7 +2645,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2693,7 +2688,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2707,10 +2702,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44928</v>
+        <v>45327</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2723,7 +2718,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2766,7 +2761,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2780,10 +2775,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45327</v>
+        <v>46062</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2796,7 +2791,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2839,7 +2834,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2853,10 +2848,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46198</v>
+        <v>45042</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2869,7 +2864,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2912,7 +2907,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2926,10 +2921,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45063</v>
+        <v>46198</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2942,7 +2937,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2985,7 +2980,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2999,10 +2994,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44930</v>
+        <v>46112</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3015,7 +3010,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3058,7 +3053,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3068,14 +3063,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45513</v>
+        <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3088,7 +3083,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3131,7 +3126,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3145,10 +3140,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45042</v>
+        <v>45327</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3161,7 +3156,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3204,7 +3199,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3218,10 +3213,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46223</v>
+        <v>45722</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3233,8 +3228,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45327</v>
+        <v>45762</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3350,7 +3350,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3360,14 +3360,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45694</v>
+        <v>45846</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46315</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2943-2023</t>
+          <t>A 11517-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1046,14 +1046,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44945</v>
+        <v>45372</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,16 +1066,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>11.3</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1090,7 +1090,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1102,148 +1102,148 @@
         <v>3</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Tvåblad
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 11517-2024 artfynd.xlsx", "A 11517-2024")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 11517-2024 karta.png", "A 11517-2024")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 11517-2024 georefererad karta.tif", "A 11517-2024")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 11517-2024 FSC-klagomål.docx", "A 11517-2024")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 11517-2024 FSC-klagomål mail.docx", "A 11517-2024")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 11517-2024 tillsynsbegäran.docx", "A 11517-2024")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 11517-2024 tillsynsbegäran mail.docx", "A 11517-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 2943-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44945</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>BÅSTAD</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Sårläka
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 2943-2023 artfynd.xlsx", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 2943-2023 karta.png", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 2943-2023 georefererad karta.tif", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 2943-2023 FSC-klagomål.docx", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 2943-2023 FSC-klagomål mail.docx", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 2943-2023 tillsynsbegäran.docx", "A 2943-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 2943-2023 tillsynsbegäran mail.docx", "A 2943-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 11517-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45372</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>BÅSTAD</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Tvåblad
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 11517-2024 artfynd.xlsx", "A 11517-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 11517-2024 karta.png", "A 11517-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 11517-2024 georefererad karta.tif", "A 11517-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 11517-2024 FSC-klagomål.docx", "A 11517-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 11517-2024 FSC-klagomål mail.docx", "A 11517-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 11517-2024 tillsynsbegäran.docx", "A 11517-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 11517-2024 tillsynsbegäran mail.docx", "A 11517-2024")</f>
         <v/>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
         <v>45209</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>45307</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44929</v>
+        <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
         <v>2.5</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1531,42 +1531,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45762</v>
+        <v>44929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1636,46 +1636,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1692,7 +1688,7 @@
         <v>45762</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1705,13 +1701,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1745,35 +1741,39 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
         <v>45055</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44957</v>
+        <v>44928</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1968,14 +1968,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45694</v>
+        <v>45327</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2031,7 +2031,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44928</v>
+        <v>45327</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2104,7 +2104,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 10710-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45063</v>
+        <v>45722</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2133,8 +2133,13 @@
           <t>BÅSTAD</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2177,7 +2182,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2191,10 +2196,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44573</v>
+        <v>45063</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2207,7 +2212,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2250,7 +2255,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2264,10 +2269,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45327</v>
+        <v>45762</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2323,7 +2328,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2333,14 +2338,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45513</v>
+        <v>45846</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2353,7 +2358,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2396,7 +2401,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2410,10 +2415,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45099</v>
+        <v>44930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2426,7 +2431,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2469,7 +2474,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2479,14 +2484,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44930</v>
+        <v>45513</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2542,7 +2547,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2556,10 +2561,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45589</v>
+        <v>45042</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2615,7 +2620,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2632,7 +2637,7 @@
         <v>45327</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2645,7 +2650,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2688,7 +2693,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2698,14 +2703,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45327</v>
+        <v>45694</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2718,7 +2723,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2761,7 +2766,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2775,10 +2780,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46062</v>
+        <v>45589</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2791,7 +2796,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2834,7 +2839,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2848,10 +2853,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45042</v>
+        <v>46062</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2864,7 +2869,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2907,7 +2912,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2921,10 +2926,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46198</v>
+        <v>46112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2937,7 +2942,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2980,7 +2985,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2994,10 +2999,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46112</v>
+        <v>45327</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3010,7 +3015,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3053,7 +3058,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31550-2026</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3067,10 +3072,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46223</v>
+        <v>45099</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3083,7 +3088,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3126,7 +3131,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3140,10 +3145,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45327</v>
+        <v>46198</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3199,7 +3204,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10710-2025</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3213,10 +3218,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45722</v>
+        <v>44957</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3228,13 +3233,8 @@
           <t>BÅSTAD</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45762</v>
+        <v>44573</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3350,7 +3350,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 31550-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45846</v>
+        <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>

--- a/Översikt BÅSTAD.xlsx
+++ b/Översikt BÅSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45565</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46315</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 11517-2024</t>
+          <t>A 2943-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1046,14 +1046,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45372</v>
+        <v>44945</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,16 +1066,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>11.3</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1090,7 +1090,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1102,148 +1102,148 @@
         <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sårläka
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 2943-2023 artfynd.xlsx", "A 2943-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 2943-2023 karta.png", "A 2943-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 2943-2023 georefererad karta.tif", "A 2943-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 2943-2023 FSC-klagomål.docx", "A 2943-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 2943-2023 FSC-klagomål mail.docx", "A 2943-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 2943-2023 tillsynsbegäran.docx", "A 2943-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 2943-2023 tillsynsbegäran mail.docx", "A 2943-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 11517-2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45372</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>BÅSTAD</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Tvåblad
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 11517-2024 artfynd.xlsx", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 11517-2024 karta.png", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 11517-2024 georefererad karta.tif", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 11517-2024 FSC-klagomål.docx", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 11517-2024 FSC-klagomål mail.docx", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 11517-2024 tillsynsbegäran.docx", "A 11517-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 11517-2024 tillsynsbegäran mail.docx", "A 11517-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 2943-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44945</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46324</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>BÅSTAD</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sårläka
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 2943-2023 artfynd.xlsx", "A 2943-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 2943-2023 karta.png", "A 2943-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 2943-2023 georefererad karta.tif", "A 2943-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 2943-2023 FSC-klagomål.docx", "A 2943-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 2943-2023 FSC-klagomål mail.docx", "A 2943-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 2943-2023 tillsynsbegäran.docx", "A 2943-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 2943-2023 tillsynsbegäran mail.docx", "A 2943-2023")</f>
         <v/>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
         <v>45209</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 1782-2024</t>
+          <t>A 389-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1366,14 +1366,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45307</v>
+        <v>44929</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
@@ -1430,38 +1430,38 @@
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18332-2025</t>
+          <t>A 18328-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1478,7 +1478,7 @@
         <v>45762</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1531,42 +1531,46 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 389-2023</t>
+          <t>A 1782-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1576,14 +1580,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44929</v>
+        <v>45307</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1596,7 +1600,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1632,7 +1636,7 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -1640,38 +1644,38 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 389-2023 artfynd.xlsx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 1782-2024 artfynd.xlsx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 389-2023 karta.png", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 1782-2024 karta.png", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 389-2023 georefererad karta.tif", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 1782-2024 georefererad karta.tif", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 389-2023 FSC-klagomål.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 1782-2024 FSC-klagomål.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 389-2023 FSC-klagomål mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 1782-2024 FSC-klagomål mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 389-2023 tillsynsbegäran.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 1782-2024 tillsynsbegäran.docx", "A 1782-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 389-2023 tillsynsbegäran mail.docx", "A 389-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 1782-2024 tillsynsbegäran mail.docx", "A 1782-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 18328-2025</t>
+          <t>A 18332-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1688,7 +1692,7 @@
         <v>45762</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1701,13 +1705,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1741,39 +1745,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18328-2025 artfynd.xlsx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/artfynd/A 18332-2025 artfynd.xlsx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18328-2025 karta.png", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor/A 18332-2025 karta.png", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18328-2025 georefererad karta.tif", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/kartor_geotiff/A 18332-2025 georefererad karta.tif", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18328-2025 FSC-klagomål.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomål/A 18332-2025 FSC-klagomål.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18328-2025 FSC-klagomål mail.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/klagomålsmail/A 18332-2025 FSC-klagomål mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18328-2025 tillsynsbegäran.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsyn/A 18332-2025 tillsynsbegäran.docx", "A 18332-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18328-2025 tillsynsbegäran mail.docx", "A 18328-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1278/fåglar/A 18328-2025 prioriterade fågelarter.docx", "A 18328-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1278/tillsynsmail/A 18332-2025 tillsynsbegäran mail.docx", "A 18332-2025")</f>
         <v/>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
         <v>45055</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24-2023</t>
+          <t>A 4481-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44928</v>
+        <v>45327</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4486-2024</t>
+          <t>A 18327-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45327</v>
+        <v>45762</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4481-2024</t>
+          <t>A 28260-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45327</v>
+        <v>45099</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2121,7 +2121,7 @@
         <v>45722</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 21572-2023</t>
+          <t>A 34400-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45063</v>
+        <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2255,7 +2255,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18327-2025</t>
+          <t>A 4822-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45762</v>
+        <v>44957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2328,7 +2328,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 34400-2025</t>
+          <t>A 1531-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45846</v>
+        <v>44573</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2401,7 +2401,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 635-2023</t>
+          <t>A 7731-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44930</v>
+        <v>46062</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2474,7 +2474,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32610-2024</t>
+          <t>A 16624-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2484,14 +2484,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45513</v>
+        <v>46112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2547,7 +2547,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 18434-2023</t>
+          <t>A 24-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45042</v>
+        <v>44928</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4487-2024</t>
+          <t>A 4486-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2637,7 +2637,7 @@
         <v>45327</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2693,7 +2693,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 5817-2025</t>
+          <t>A 21572-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2703,14 +2703,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45694</v>
+        <v>45063</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2766,7 +2766,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 48181-2024</t>
+          <t>A 635-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45589</v>
+        <v>44930</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 7731-2026</t>
+          <t>A 32610-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2849,14 +2849,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46062</v>
+        <v>45513</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16624-2026</t>
+          <t>A 18434-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46112</v>
+        <v>45042</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 4493-2024</t>
+          <t>A 4487-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3002,7 +3002,7 @@
         <v>45327</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3058,7 +3058,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 28260-2023</t>
+          <t>A 5817-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3068,14 +3068,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45099</v>
+        <v>45694</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3131,7 +3131,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 28854-2026</t>
+          <t>A 48181-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46198</v>
+        <v>45589</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3204,7 +3204,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4822-2023</t>
+          <t>A 4493-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44957</v>
+        <v>45327</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 1531-2022</t>
+          <t>A 28854-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44573</v>
+        <v>46198</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3367,7 +3367,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
